--- a/artfynd/A 26840-2026 artfynd.xlsx
+++ b/artfynd/A 26840-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>103081158</v>
       </c>
       <c r="B2" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>619170.8882562279</v>
+        <v>619171</v>
       </c>
       <c r="R2" t="n">
-        <v>6344202.141907326</v>
+        <v>6344202</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2020-12-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-12-17</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -803,12 +788,7 @@
         <v>103081160</v>
       </c>
       <c r="B3" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>619160.8607966517</v>
+        <v>619161</v>
       </c>
       <c r="R3" t="n">
-        <v>6344211.059502125</v>
+        <v>6344211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -882,19 +862,9 @@
           <t>2020-12-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-12-17</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -928,12 +898,7 @@
         <v>103178791</v>
       </c>
       <c r="B4" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>619155.0683137478</v>
+        <v>619155</v>
       </c>
       <c r="R4" t="n">
-        <v>6344204.933457104</v>
+        <v>6344205</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1007,19 +972,9 @@
           <t>2020-12-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-12-17</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1039,7 +994,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Thomas Johansson, David Bartholdsson</t>
+          <t>Thomas Johansson, Vide Kindgren Bartholdsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">

--- a/artfynd/A 26840-2026 artfynd.xlsx
+++ b/artfynd/A 26840-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081158</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103081160</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,8 +1017,18 @@
           <t>Trädportalen</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/103178791</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>